--- a/Avaliações dos Itens/Pré-teste (2003 - 2007)/2006.xlsx
+++ b/Avaliações dos Itens/Pré-teste (2003 - 2007)/2006.xlsx
@@ -1,16 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1a040bb1f01841a5/Desktop/Educomp 2026/Análises/Avaliação 1/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{4D9A3B02-1CD0-404D-AB4F-A7A7E99A1D93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{465EC308-6F1F-48B5-94C2-D16EB945717D}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{4D9A3B02-1CD0-404D-AB4F-A7A7E99A1D93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{760DACE4-A3DD-403C-A507-FC20425548DB}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{FDB43484-E608-44ED-AFC7-72B29FACA779}"/>
+    <workbookView xWindow="30597" yWindow="1129" windowWidth="22119" windowHeight="11612" xr2:uid="{FDB43484-E608-44ED-AFC7-72B29FACA779}"/>
   </bookViews>
   <sheets>
     <sheet name="2006" sheetId="1" r:id="rId1"/>
@@ -475,9 +470,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A1508FB-1BB0-4F41-94DB-083700318396}">
   <dimension ref="A1:E102"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>2</v>
       </c>
@@ -494,7 +489,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -511,7 +506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -528,7 +523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -545,7 +540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
@@ -562,7 +557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>0</v>
       </c>
@@ -579,7 +574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
@@ -596,7 +591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>1</v>
       </c>
@@ -613,7 +608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>1</v>
       </c>
@@ -630,7 +625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>1</v>
       </c>
@@ -647,7 +642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>0</v>
       </c>
@@ -664,7 +659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>0</v>
       </c>
@@ -681,7 +676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>0</v>
       </c>
@@ -698,7 +693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>0</v>
       </c>
@@ -715,7 +710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>0</v>
       </c>
@@ -732,7 +727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>0</v>
       </c>
@@ -749,7 +744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>0</v>
       </c>
@@ -766,152 +761,153 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="D74" s="2"/>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="D75" s="2"/>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="D76" s="2"/>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="D77" s="2"/>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="D78" s="2"/>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="D79" s="2"/>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="D80" s="2"/>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="D81" s="2"/>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="D82" s="2"/>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="D83" s="2"/>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="D84" s="2"/>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="D85" s="2"/>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="D86" s="2"/>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="D87" s="2"/>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="D88" s="2"/>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="D89" s="2"/>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="D90" s="2"/>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="D91" s="2"/>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="D92" s="2"/>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="D93" s="2"/>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="D94" s="2"/>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="D95" s="2"/>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="D96" s="2"/>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="D97" s="2"/>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="D98" s="2"/>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="D99" s="2"/>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="D100" s="2"/>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="D101" s="2"/>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="D102" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>